--- a/연구코드/results/regression/sinchon/male/regression_results.xlsx
+++ b/연구코드/results/regression/sinchon/male/regression_results.xlsx
@@ -557,13 +557,13 @@
         <v>0.0484</v>
       </c>
       <c r="M2">
-        <v>0.793</v>
+        <v>0.702</v>
       </c>
       <c r="N2">
-        <v>0.3226</v>
+        <v>0.8323</v>
       </c>
       <c r="O2">
-        <v>0.9439</v>
+        <v>0.6601</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -604,13 +604,13 @@
         <v>0.0398</v>
       </c>
       <c r="M3">
-        <v>0.7883</v>
+        <v>0.7305</v>
       </c>
       <c r="N3">
-        <v>0.3097</v>
+        <v>0.7548</v>
       </c>
       <c r="O3">
-        <v>0.9419</v>
+        <v>0.7229</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -651,13 +651,13 @@
         <v>0.0367</v>
       </c>
       <c r="M4">
-        <v>0.7852</v>
+        <v>0.7036</v>
       </c>
       <c r="N4">
-        <v>0.2903</v>
+        <v>0.7935</v>
       </c>
       <c r="O4">
-        <v>0.944</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -698,13 +698,13 @@
         <v>0.0411</v>
       </c>
       <c r="M5">
-        <v>0.7617</v>
+        <v>0.743</v>
       </c>
       <c r="N5">
-        <v>0.2903</v>
+        <v>0.7484</v>
       </c>
       <c r="O5">
-        <v>0.9129</v>
+        <v>0.7413999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -745,13 +745,13 @@
         <v>0.0483</v>
       </c>
       <c r="M6">
-        <v>0.7664</v>
+        <v>0.7399</v>
       </c>
       <c r="N6">
-        <v>0.2839</v>
+        <v>0.7419</v>
       </c>
       <c r="O6">
-        <v>0.9211</v>
+        <v>0.7393999999999999</v>
       </c>
     </row>
   </sheetData>
